--- a/academias/Matemáticas - Estadisticos 20232.xlsx
+++ b/academias/Matemáticas - Estadisticos 20232.xlsx
@@ -2418,25 +2418,25 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2453,25 +2453,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2488,25 +2488,25 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2523,25 +2523,25 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2558,25 +2558,25 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2590,25 +2590,25 @@
         <v>112</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F7">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>18.8</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2625,25 +2625,25 @@
         <v>42</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2657,25 +2657,25 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2692,25 +2692,25 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2727,25 +2727,25 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J11">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2759,25 +2759,25 @@
         <v>63</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F12">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>7.9</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J12">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2794,25 +2794,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>23.3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2829,25 +2829,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2864,25 +2864,25 @@
         <v>26</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J15">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2899,25 +2899,25 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>35.7</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2931,25 +2931,25 @@
         <v>94</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F17">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>21.3</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2966,25 +2966,25 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>54.8</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>45.2</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J18">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3001,25 +3001,25 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>23.8</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3036,25 +3036,25 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3071,25 +3071,25 @@
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3103,25 +3103,25 @@
         <v>107</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F22">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>75.7</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>24.3</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J22">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3138,25 +3138,25 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>48.3</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>51.7</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3173,25 +3173,25 @@
         <v>23</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F24">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>60.9</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>39.1</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3208,25 +3208,25 @@
         <v>12</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -3243,25 +3243,25 @@
         <v>15</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>13.3</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3275,25 +3275,25 @@
         <v>79</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F27">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>60.8</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>39.2</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3310,25 +3310,25 @@
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>23.3</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J28">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3345,25 +3345,25 @@
         <v>23</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J29">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3377,25 +3377,25 @@
         <v>53</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F30">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>18.9</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3412,25 +3412,25 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>23.1</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J31">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3447,25 +3447,25 @@
         <v>31</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F32">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J32">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3482,25 +3482,25 @@
         <v>35</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F33">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>31.4</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J33">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3517,25 +3517,25 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>20.8</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J34">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3552,25 +3552,25 @@
         <v>38</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F35">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>76.3</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>23.7</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J35">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3587,25 +3587,25 @@
         <v>29</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>55.2</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>44.8</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J36">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3622,25 +3622,25 @@
         <v>35</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>22.9</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3657,25 +3657,25 @@
         <v>45</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F38">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>31.1</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J38">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3692,25 +3692,25 @@
         <v>31</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F39">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>67.7</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>32.3</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J39">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3724,25 +3724,25 @@
         <v>307</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="F40">
-        <v>307</v>
+        <v>84</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>27.4</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J40">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3759,25 +3759,25 @@
         <v>28</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F41">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="H41" s="1">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J41">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3791,25 +3791,25 @@
         <v>28</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="H42" s="1">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J42">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3826,25 +3826,25 @@
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F43">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H43" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I43" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J43">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3861,25 +3861,25 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F44">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J44">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3896,25 +3896,25 @@
         <v>24</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F45">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H45" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I45" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J45">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3931,25 +3931,25 @@
         <v>31</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F46">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I46" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J46">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3966,25 +3966,25 @@
         <v>28</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F47">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H47" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I47" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J47">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4001,25 +4001,25 @@
         <v>37</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F48">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H48" s="1">
-        <v>100</v>
+        <v>8.1</v>
       </c>
       <c r="I48" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J48">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4033,25 +4033,25 @@
         <v>187</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F49">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H49" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="I49" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J49">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4068,25 +4068,25 @@
         <v>33</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F50">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>39.4</v>
       </c>
       <c r="H50" s="1">
-        <v>100</v>
+        <v>60.6</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J50">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4100,25 +4100,25 @@
         <v>33</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F51">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>39.4</v>
       </c>
       <c r="H51" s="1">
-        <v>100</v>
+        <v>60.6</v>
       </c>
       <c r="I51" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J51">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4129,25 +4129,25 @@
         <v>1105</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="F52">
-        <v>1105</v>
+        <v>247</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H52" s="1">
-        <v>100</v>
+        <v>22.4</v>
       </c>
       <c r="I52" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J52">
-        <v>1105</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4215,19 +4215,19 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>69.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>30.8</v>
+        <v>26.9</v>
       </c>
       <c r="I2" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -4250,19 +4250,19 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>71.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>6.7</v>
       </c>
       <c r="I4" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -4355,19 +4355,19 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="I6" s="2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -4387,19 +4387,19 @@
         <v>112</v>
       </c>
       <c r="E7">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1">
-        <v>77.7</v>
+        <v>81.2</v>
       </c>
       <c r="H7" s="1">
-        <v>22.3</v>
+        <v>18.8</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>2.4</v>
       </c>
       <c r="I8" s="2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -4466,7 +4466,7 @@
         <v>2.4</v>
       </c>
       <c r="I9" s="2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -4489,19 +4489,19 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H10" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4524,19 +4524,19 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>92.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="H11" s="1">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
       <c r="I11" s="2">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4556,16 +4556,16 @@
         <v>63</v>
       </c>
       <c r="E12">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>93.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="I12" s="2">
         <v>8.6</v>
@@ -4591,19 +4591,19 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>70</v>
+        <v>76.7</v>
       </c>
       <c r="H13" s="1">
-        <v>30</v>
+        <v>23.3</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4638,7 +4638,7 @@
         <v>4.2</v>
       </c>
       <c r="I14" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4661,19 +4661,19 @@
         <v>26</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>76.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>23.1</v>
+        <v>26.9</v>
       </c>
       <c r="I15" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4696,16 +4696,16 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>71.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="H16" s="1">
-        <v>28.6</v>
+        <v>35.7</v>
       </c>
       <c r="I16" s="2">
         <v>7.6</v>
@@ -4763,19 +4763,19 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="H18" s="1">
-        <v>41.9</v>
+        <v>45.2</v>
       </c>
       <c r="I18" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4798,19 +4798,19 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>61.9</v>
+        <v>76.2</v>
       </c>
       <c r="H19" s="1">
-        <v>38.1</v>
+        <v>23.8</v>
       </c>
       <c r="I19" s="2">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4833,19 +4833,19 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H20" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I20" s="2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4868,19 +4868,19 @@
         <v>30</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H21" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I21" s="2">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4900,19 +4900,19 @@
         <v>107</v>
       </c>
       <c r="E22">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F22">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G22" s="1">
-        <v>70.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H22" s="1">
-        <v>29.9</v>
+        <v>24.3</v>
       </c>
       <c r="I22" s="2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4947,7 +4947,7 @@
         <v>51.7</v>
       </c>
       <c r="I23" s="2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4970,16 +4970,16 @@
         <v>23</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G24" s="1">
-        <v>65.2</v>
+        <v>60.9</v>
       </c>
       <c r="H24" s="1">
-        <v>34.8</v>
+        <v>39.1</v>
       </c>
       <c r="I24" s="2">
         <v>5.7</v>
@@ -5017,7 +5017,7 @@
         <v>41.7</v>
       </c>
       <c r="I25" s="2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -5040,19 +5040,19 @@
         <v>15</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="H26" s="1">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="I26" s="2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -5072,16 +5072,16 @@
         <v>79</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F27">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G27" s="1">
-        <v>63.3</v>
+        <v>60.8</v>
       </c>
       <c r="H27" s="1">
-        <v>36.7</v>
+        <v>39.2</v>
       </c>
       <c r="I27" s="2">
         <v>6</v>
@@ -5107,19 +5107,19 @@
         <v>30</v>
       </c>
       <c r="E28">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" s="1">
-        <v>86.7</v>
+        <v>76.7</v>
       </c>
       <c r="H28" s="1">
-        <v>13.3</v>
+        <v>23.3</v>
       </c>
       <c r="I28" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>53</v>
       </c>
       <c r="E30">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G30" s="1">
-        <v>86.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>13.2</v>
+        <v>18.9</v>
       </c>
       <c r="I30" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5209,19 +5209,19 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>84.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>15.4</v>
+        <v>23.1</v>
       </c>
       <c r="I31" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -5244,19 +5244,19 @@
         <v>31</v>
       </c>
       <c r="E32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1">
-        <v>87.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H32" s="1">
-        <v>12.9</v>
+        <v>16.1</v>
       </c>
       <c r="I32" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -5279,19 +5279,19 @@
         <v>35</v>
       </c>
       <c r="E33">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G33" s="1">
-        <v>77.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>22.9</v>
+        <v>31.4</v>
       </c>
       <c r="I33" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5314,19 +5314,19 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1">
-        <v>83.3</v>
+        <v>79.2</v>
       </c>
       <c r="H34" s="1">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="I34" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5349,19 +5349,19 @@
         <v>38</v>
       </c>
       <c r="E35">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G35" s="1">
-        <v>84.2</v>
+        <v>76.3</v>
       </c>
       <c r="H35" s="1">
-        <v>15.8</v>
+        <v>23.7</v>
       </c>
       <c r="I35" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -5384,19 +5384,19 @@
         <v>29</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36" s="1">
-        <v>51.7</v>
+        <v>55.2</v>
       </c>
       <c r="H36" s="1">
-        <v>48.3</v>
+        <v>44.8</v>
       </c>
       <c r="I36" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5419,19 +5419,19 @@
         <v>35</v>
       </c>
       <c r="E37">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>54.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H37" s="1">
-        <v>45.7</v>
+        <v>22.9</v>
       </c>
       <c r="I37" s="2">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -5454,19 +5454,19 @@
         <v>45</v>
       </c>
       <c r="E38">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F38">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G38" s="1">
-        <v>55.6</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>44.4</v>
+        <v>31.1</v>
       </c>
       <c r="I38" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -5489,19 +5489,19 @@
         <v>31</v>
       </c>
       <c r="E39">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F39">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G39" s="1">
-        <v>61.3</v>
+        <v>67.7</v>
       </c>
       <c r="H39" s="1">
-        <v>38.7</v>
+        <v>32.3</v>
       </c>
       <c r="I39" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -5521,19 +5521,19 @@
         <v>307</v>
       </c>
       <c r="E40">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F40">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G40" s="1">
-        <v>70.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H40" s="1">
-        <v>29.3</v>
+        <v>27.4</v>
       </c>
       <c r="I40" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -5556,19 +5556,19 @@
         <v>28</v>
       </c>
       <c r="E41">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G41" s="1">
-        <v>64.3</v>
+        <v>57.1</v>
       </c>
       <c r="H41" s="1">
-        <v>35.7</v>
+        <v>42.9</v>
       </c>
       <c r="I41" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -5588,19 +5588,19 @@
         <v>28</v>
       </c>
       <c r="E42">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G42" s="1">
-        <v>64.3</v>
+        <v>57.1</v>
       </c>
       <c r="H42" s="1">
-        <v>35.7</v>
+        <v>42.9</v>
       </c>
       <c r="I42" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -5623,19 +5623,19 @@
         <v>30</v>
       </c>
       <c r="E43">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G43" s="1">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="H43" s="1">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="I43" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5658,19 +5658,19 @@
         <v>37</v>
       </c>
       <c r="E44">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H44" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I45" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -5763,19 +5763,19 @@
         <v>28</v>
       </c>
       <c r="E47">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F47">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G47" s="1">
-        <v>67.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H47" s="1">
-        <v>32.1</v>
+        <v>25</v>
       </c>
       <c r="I47" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -5810,7 +5810,7 @@
         <v>8.1</v>
       </c>
       <c r="I48" s="2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -5830,19 +5830,19 @@
         <v>187</v>
       </c>
       <c r="E49">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F49">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G49" s="1">
-        <v>89.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H49" s="1">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="I49" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -5865,19 +5865,19 @@
         <v>33</v>
       </c>
       <c r="E50">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F50">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G50" s="1">
-        <v>24.2</v>
+        <v>39.4</v>
       </c>
       <c r="H50" s="1">
-        <v>75.8</v>
+        <v>60.6</v>
       </c>
       <c r="I50" s="2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -5897,19 +5897,19 @@
         <v>33</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F51">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G51" s="1">
-        <v>24.2</v>
+        <v>39.4</v>
       </c>
       <c r="H51" s="1">
-        <v>75.8</v>
+        <v>60.6</v>
       </c>
       <c r="I51" s="2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -5926,19 +5926,19 @@
         <v>1105</v>
       </c>
       <c r="E52">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="F52">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="G52" s="1">
-        <v>76.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H52" s="1">
-        <v>23.7</v>
+        <v>22.4</v>
       </c>
       <c r="I52" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J52">
         <v>0</v>

--- a/academias/Matemáticas - Estadisticos 20232.xlsx
+++ b/academias/Matemáticas - Estadisticos 20232.xlsx
@@ -758,22 +758,22 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="H6" s="1">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="I6" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -790,19 +790,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F7">
         <v>25</v>
       </c>
       <c r="G7" s="1">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="I7" s="2">
         <v>7.1</v>
@@ -1099,22 +1099,22 @@
         <v>32</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H16" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I16" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1131,19 +1131,19 @@
         <v>24</v>
       </c>
       <c r="D17">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E17">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17">
         <v>20</v>
       </c>
       <c r="G17" s="1">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="I17" s="2">
         <v>7.8</v>
@@ -2131,10 +2131,10 @@
         <v>58</v>
       </c>
       <c r="D46">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E46">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2233,19 +2233,19 @@
         <v>24</v>
       </c>
       <c r="D49">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E49">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F49">
         <v>19</v>
       </c>
       <c r="G49" s="1">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H49" s="1">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="I49" s="2">
         <v>7.7</v>
@@ -2329,19 +2329,19 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="E52">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="F52">
         <v>262</v>
       </c>
       <c r="G52" s="1">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H52" s="1">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>
@@ -2555,22 +2555,22 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>71.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H6" s="1">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2587,22 +2587,22 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F7">
         <v>21</v>
       </c>
       <c r="G7" s="1">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2896,22 +2896,22 @@
         <v>32</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16">
         <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="H16" s="1">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="I16" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2928,22 +2928,22 @@
         <v>24</v>
       </c>
       <c r="D17">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E17">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17">
         <v>20</v>
       </c>
       <c r="G17" s="1">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="I17" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3928,10 +3928,10 @@
         <v>58</v>
       </c>
       <c r="D46">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E46">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -4030,19 +4030,19 @@
         <v>24</v>
       </c>
       <c r="D49">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E49">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F49">
         <v>17</v>
       </c>
       <c r="G49" s="1">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="H49" s="1">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I49" s="2">
         <v>8</v>
@@ -4126,19 +4126,19 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="E52">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="F52">
         <v>247</v>
       </c>
       <c r="G52" s="1">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="H52" s="1">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="I52" s="2">
         <v>7.3</v>
@@ -4215,19 +4215,19 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>96.2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="I2" s="2">
         <v>7</v>
-      </c>
-      <c r="G2" s="1">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="H2" s="1">
-        <v>26.9</v>
-      </c>
-      <c r="I2" s="2">
-        <v>6.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>75</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>25</v>
+        <v>3.1</v>
       </c>
       <c r="I3" s="2">
         <v>6.9</v>
@@ -4297,7 +4297,7 @@
         <v>6.7</v>
       </c>
       <c r="I4" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
         <v>7.8</v>
@@ -4352,22 +4352,22 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="H6" s="1">
-        <v>28.6</v>
+        <v>13.3</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>81.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>18.8</v>
+        <v>4.4</v>
       </c>
       <c r="I7" s="2">
         <v>7.3</v>
@@ -4489,19 +4489,19 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H10" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>5.3</v>
       </c>
       <c r="I11" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4556,16 +4556,16 @@
         <v>63</v>
       </c>
       <c r="E12">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>92.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H12" s="1">
-        <v>7.9</v>
+        <v>4.8</v>
       </c>
       <c r="I12" s="2">
         <v>8.6</v>
@@ -4591,19 +4591,19 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>76.7</v>
+        <v>90</v>
       </c>
       <c r="H13" s="1">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4661,19 +4661,19 @@
         <v>26</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>73.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4693,22 +4693,22 @@
         <v>32</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>64.3</v>
+        <v>73.3</v>
       </c>
       <c r="H16" s="1">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
       <c r="I16" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4725,22 +4725,22 @@
         <v>24</v>
       </c>
       <c r="D17">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E17">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1">
-        <v>78.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>21.3</v>
+        <v>8.4</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4763,19 +4763,19 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>54.8</v>
+        <v>90.3</v>
       </c>
       <c r="H18" s="1">
-        <v>45.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I18" s="2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4798,19 +4798,19 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>76.2</v>
+        <v>85.7</v>
       </c>
       <c r="H19" s="1">
-        <v>23.8</v>
+        <v>14.3</v>
       </c>
       <c r="I19" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>4</v>
       </c>
       <c r="I20" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4868,19 +4868,19 @@
         <v>30</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>80</v>
+        <v>93.3</v>
       </c>
       <c r="H21" s="1">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="I21" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4900,19 +4900,19 @@
         <v>107</v>
       </c>
       <c r="E22">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G22" s="1">
-        <v>75.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>24.3</v>
+        <v>8.4</v>
       </c>
       <c r="I22" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4935,19 +4935,19 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" s="1">
-        <v>48.3</v>
+        <v>44.8</v>
       </c>
       <c r="H23" s="1">
-        <v>51.7</v>
+        <v>55.2</v>
       </c>
       <c r="I23" s="2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -5005,19 +5005,19 @@
         <v>12</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>58.3</v>
+        <v>75</v>
       </c>
       <c r="H25" s="1">
-        <v>41.7</v>
+        <v>25</v>
       </c>
       <c r="I25" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>13.3</v>
       </c>
       <c r="I26" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -5072,19 +5072,19 @@
         <v>79</v>
       </c>
       <c r="E27">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F27">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1">
-        <v>60.8</v>
+        <v>62</v>
       </c>
       <c r="H27" s="1">
-        <v>39.2</v>
+        <v>38</v>
       </c>
       <c r="I27" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>30</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="H28" s="1">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="I28" s="2">
         <v>7</v>
@@ -5142,19 +5142,19 @@
         <v>23</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>87</v>
+        <v>95.7</v>
       </c>
       <c r="H29" s="1">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="I29" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         <v>53</v>
       </c>
       <c r="E30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G30" s="1">
-        <v>81.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="H30" s="1">
-        <v>18.9</v>
+        <v>11.3</v>
       </c>
       <c r="I30" s="2">
         <v>7.2</v>
@@ -5209,16 +5209,16 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31" s="1">
-        <v>76.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H31" s="1">
-        <v>23.1</v>
+        <v>20.5</v>
       </c>
       <c r="I31" s="2">
         <v>6.7</v>
@@ -5244,19 +5244,19 @@
         <v>31</v>
       </c>
       <c r="E32">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G32" s="1">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="H32" s="1">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I32" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -5279,19 +5279,19 @@
         <v>35</v>
       </c>
       <c r="E33">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F33">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1">
-        <v>68.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H33" s="1">
-        <v>31.4</v>
+        <v>14.3</v>
       </c>
       <c r="I33" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5314,16 +5314,16 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1">
-        <v>79.2</v>
+        <v>95.8</v>
       </c>
       <c r="H34" s="1">
-        <v>20.8</v>
+        <v>4.2</v>
       </c>
       <c r="I34" s="2">
         <v>6.9</v>
@@ -5349,19 +5349,19 @@
         <v>38</v>
       </c>
       <c r="E35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>76.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H35" s="1">
-        <v>23.7</v>
+        <v>18.4</v>
       </c>
       <c r="I35" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -5384,19 +5384,19 @@
         <v>29</v>
       </c>
       <c r="E36">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F36">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>55.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H36" s="1">
-        <v>44.8</v>
+        <v>3.4</v>
       </c>
       <c r="I36" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5419,19 +5419,19 @@
         <v>35</v>
       </c>
       <c r="E37">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1">
-        <v>77.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H37" s="1">
-        <v>22.9</v>
+        <v>14.3</v>
       </c>
       <c r="I37" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -5489,19 +5489,19 @@
         <v>31</v>
       </c>
       <c r="E39">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G39" s="1">
-        <v>67.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H39" s="1">
-        <v>32.3</v>
+        <v>12.9</v>
       </c>
       <c r="I39" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -5521,16 +5521,16 @@
         <v>307</v>
       </c>
       <c r="E40">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="F40">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="G40" s="1">
-        <v>72.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H40" s="1">
-        <v>27.4</v>
+        <v>15.6</v>
       </c>
       <c r="I40" s="2">
         <v>6.8</v>
@@ -5556,16 +5556,16 @@
         <v>28</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G41" s="1">
-        <v>57.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H41" s="1">
-        <v>42.9</v>
+        <v>21.4</v>
       </c>
       <c r="I41" s="2">
         <v>6.7</v>
@@ -5588,16 +5588,16 @@
         <v>28</v>
       </c>
       <c r="E42">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F42">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G42" s="1">
-        <v>57.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>42.9</v>
+        <v>21.4</v>
       </c>
       <c r="I42" s="2">
         <v>6.7</v>
@@ -5623,19 +5623,19 @@
         <v>30</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H43" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I43" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5693,16 +5693,16 @@
         <v>24</v>
       </c>
       <c r="E45">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H45" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I45" s="2">
         <v>8.4</v>
@@ -5725,10 +5725,10 @@
         <v>58</v>
       </c>
       <c r="D46">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E46">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -5763,19 +5763,19 @@
         <v>28</v>
       </c>
       <c r="E47">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F47">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H47" s="1">
-        <v>25</v>
+        <v>3.6</v>
       </c>
       <c r="I47" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -5798,19 +5798,19 @@
         <v>37</v>
       </c>
       <c r="E48">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H48" s="1">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -5827,22 +5827,22 @@
         <v>24</v>
       </c>
       <c r="D49">
+        <v>189</v>
+      </c>
+      <c r="E49">
         <v>187</v>
       </c>
-      <c r="E49">
-        <v>170</v>
-      </c>
       <c r="F49">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1">
-        <v>90.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H49" s="1">
-        <v>9.1</v>
+        <v>1.1</v>
       </c>
       <c r="I49" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -5865,19 +5865,19 @@
         <v>33</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F50">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G50" s="1">
-        <v>39.4</v>
+        <v>78.8</v>
       </c>
       <c r="H50" s="1">
-        <v>60.6</v>
+        <v>21.2</v>
       </c>
       <c r="I50" s="2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -5897,19 +5897,19 @@
         <v>33</v>
       </c>
       <c r="E51">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F51">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G51" s="1">
-        <v>39.4</v>
+        <v>78.8</v>
       </c>
       <c r="H51" s="1">
-        <v>60.6</v>
+        <v>21.2</v>
       </c>
       <c r="I51" s="2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -5923,19 +5923,19 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="E52">
-        <v>858</v>
+        <v>984</v>
       </c>
       <c r="F52">
-        <v>247</v>
+        <v>125</v>
       </c>
       <c r="G52" s="1">
-        <v>77.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="H52" s="1">
-        <v>22.4</v>
+        <v>11.3</v>
       </c>
       <c r="I52" s="2">
         <v>7.3</v>
